--- a/data/EPRB.MI.xlsx
+++ b/data/EPRB.MI.xlsx
@@ -22153,6 +22153,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="948">
+      <c r="A948" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B948" t="n">
+        <v>4200</v>
+      </c>
+      <c r="C948" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="D948" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="E948" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="F948" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="G948" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EPRB.MI.xlsx
+++ b/data/EPRB.MI.xlsx
@@ -22176,6 +22176,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="949">
+      <c r="A949" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B949" t="n">
+        <v>0</v>
+      </c>
+      <c r="C949" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="D949" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="E949" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="F949" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="G949" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EPRB.MI.xlsx
+++ b/data/EPRB.MI.xlsx
@@ -22199,6 +22199,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="950">
+      <c r="A950" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B950" t="n">
+        <v>0</v>
+      </c>
+      <c r="C950" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="D950" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="E950" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="F950" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="G950" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EPRB.MI.xlsx
+++ b/data/EPRB.MI.xlsx
@@ -22063,7 +22063,7 @@
     </row>
     <row r="944">
       <c r="A944" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B944" t="n">
         <v>0</v>
@@ -22086,22 +22086,22 @@
     </row>
     <row r="945">
       <c r="A945" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B945" t="n">
-        <v>1400</v>
+        <v>0</v>
       </c>
       <c r="C945" t="n">
-        <v>1.20000004768372</v>
+        <v>1.17999994754791</v>
       </c>
       <c r="D945" t="n">
-        <v>1.15499997138977</v>
+        <v>1.17999994754791</v>
       </c>
       <c r="E945" t="n">
-        <v>1.20000004768372</v>
+        <v>1.17999994754791</v>
       </c>
       <c r="F945" t="n">
-        <v>1.15499997138977</v>
+        <v>1.17999994754791</v>
       </c>
       <c r="G945" t="s">
         <v>7</v>
@@ -22109,22 +22109,22 @@
     </row>
     <row r="946">
       <c r="A946" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B946" t="n">
-        <v>1050</v>
+        <v>1400</v>
       </c>
       <c r="C946" t="n">
-        <v>1.13999998569489</v>
+        <v>1.20000004768372</v>
       </c>
       <c r="D946" t="n">
-        <v>1.13499999046326</v>
+        <v>1.15499997138977</v>
       </c>
       <c r="E946" t="n">
-        <v>1.13999998569489</v>
+        <v>1.20000004768372</v>
       </c>
       <c r="F946" t="n">
-        <v>1.13499999046326</v>
+        <v>1.15499997138977</v>
       </c>
       <c r="G946" t="s">
         <v>7</v>
@@ -22132,22 +22132,22 @@
     </row>
     <row r="947">
       <c r="A947" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B947" t="n">
-        <v>700</v>
+        <v>1050</v>
       </c>
       <c r="C947" t="n">
-        <v>1.19500005245209</v>
+        <v>1.13999998569489</v>
       </c>
       <c r="D947" t="n">
-        <v>1.19500005245209</v>
+        <v>1.13499999046326</v>
       </c>
       <c r="E947" t="n">
-        <v>1.19500005245209</v>
+        <v>1.13999998569489</v>
       </c>
       <c r="F947" t="n">
-        <v>1.19500005245209</v>
+        <v>1.13499999046326</v>
       </c>
       <c r="G947" t="s">
         <v>7</v>
@@ -22155,22 +22155,22 @@
     </row>
     <row r="948">
       <c r="A948" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B948" t="n">
-        <v>4200</v>
+        <v>700</v>
       </c>
       <c r="C948" t="n">
-        <v>1.16999995708466</v>
+        <v>1.19500005245209</v>
       </c>
       <c r="D948" t="n">
-        <v>1.1599999666214</v>
+        <v>1.19500005245209</v>
       </c>
       <c r="E948" t="n">
-        <v>1.16999995708466</v>
+        <v>1.19500005245209</v>
       </c>
       <c r="F948" t="n">
-        <v>1.1599999666214</v>
+        <v>1.19500005245209</v>
       </c>
       <c r="G948" t="s">
         <v>7</v>
@@ -22178,19 +22178,19 @@
     </row>
     <row r="949">
       <c r="A949" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B949" t="n">
-        <v>0</v>
+        <v>4200</v>
       </c>
       <c r="C949" t="n">
-        <v>1.1599999666214</v>
+        <v>1.16999995708466</v>
       </c>
       <c r="D949" t="n">
         <v>1.1599999666214</v>
       </c>
       <c r="E949" t="n">
-        <v>1.1599999666214</v>
+        <v>1.16999995708466</v>
       </c>
       <c r="F949" t="n">
         <v>1.1599999666214</v>
@@ -22201,7 +22201,7 @@
     </row>
     <row r="950">
       <c r="A950" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B950" t="n">
         <v>0</v>
@@ -22219,6 +22219,52 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G950" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B951" t="n">
+        <v>0</v>
+      </c>
+      <c r="C951" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="D951" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="E951" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="F951" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="G951" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B952" t="n">
+        <v>2100</v>
+      </c>
+      <c r="C952" t="n">
+        <v>1.17999994754791</v>
+      </c>
+      <c r="D952" t="n">
+        <v>1.17999994754791</v>
+      </c>
+      <c r="E952" t="n">
+        <v>1.17999994754791</v>
+      </c>
+      <c r="F952" t="n">
+        <v>1.17999994754791</v>
+      </c>
+      <c r="G952" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/EPRB.MI.xlsx
+++ b/data/EPRB.MI.xlsx
@@ -22247,24 +22247,47 @@
     </row>
     <row r="952">
       <c r="A952" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B952" t="n">
+        <v>0</v>
+      </c>
+      <c r="C952" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="D952" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="E952" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="F952" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="G952" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" s="1" t="n">
         <v>46283.2916666667</v>
       </c>
-      <c r="B952" t="n">
+      <c r="B953" t="n">
         <v>2100</v>
       </c>
-      <c r="C952" t="n">
+      <c r="C953" t="n">
         <v>1.17999994754791</v>
       </c>
-      <c r="D952" t="n">
+      <c r="D953" t="n">
         <v>1.17999994754791</v>
       </c>
-      <c r="E952" t="n">
+      <c r="E953" t="n">
         <v>1.17999994754791</v>
       </c>
-      <c r="F952" t="n">
+      <c r="F953" t="n">
         <v>1.17999994754791</v>
       </c>
-      <c r="G952" t="s">
+      <c r="G953" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/EPRB.MI.xlsx
+++ b/data/EPRB.MI.xlsx
@@ -22291,6 +22291,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="954">
+      <c r="A954" s="1" t="n">
+        <v>46286.2916666667</v>
+      </c>
+      <c r="B954" t="n">
+        <v>0</v>
+      </c>
+      <c r="C954" t="n">
+        <v>1.17999994754791</v>
+      </c>
+      <c r="D954" t="n">
+        <v>1.17999994754791</v>
+      </c>
+      <c r="E954" t="n">
+        <v>1.17999994754791</v>
+      </c>
+      <c r="F954" t="n">
+        <v>1.17999994754791</v>
+      </c>
+      <c r="G954" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EPRB.MI.xlsx
+++ b/data/EPRB.MI.xlsx
@@ -25231,6 +25231,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="957">
+      <c r="A957" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B957" t="n">
+        <v>1400</v>
+      </c>
+      <c r="C957" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="D957" t="n">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="E957" t="n">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="F957" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="G957" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="H957" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EPRB.MI.xlsx
+++ b/data/EPRB.MI.xlsx
@@ -22383,6 +22383,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="958">
+      <c r="A958" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B958" t="n">
+        <v>0</v>
+      </c>
+      <c r="C958" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="D958" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="E958" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="F958" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="G958" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" s="1" t="n">
+        <v>46293.2916666667</v>
+      </c>
+      <c r="B959" t="n">
+        <v>5250</v>
+      </c>
+      <c r="C959" t="n">
+        <v>1.17999994754791</v>
+      </c>
+      <c r="D959" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="E959" t="n">
+        <v>1.17999994754791</v>
+      </c>
+      <c r="F959"/>
+      <c r="G959" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EPRB.MI.xlsx
+++ b/data/EPRB.MI.xlsx
@@ -25335,6 +25335,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="961">
+      <c r="A961" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B961" t="n">
+        <v>38150</v>
+      </c>
+      <c r="C961" t="n">
+        <v>1.36500000953674</v>
+      </c>
+      <c r="D961" t="n">
+        <v>1.26999998092651</v>
+      </c>
+      <c r="E961" t="n">
+        <v>1.28999996185303</v>
+      </c>
+      <c r="F961" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="G961" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="H961" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EPRB.MI.xlsx
+++ b/data/EPRB.MI.xlsx
@@ -22537,8 +22537,31 @@
       <c r="E964" t="n">
         <v>1.2150000333786</v>
       </c>
-      <c r="F964"/>
+      <c r="F964" t="n">
+        <v>1.20000004768372</v>
+      </c>
       <c r="G964" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B965" t="n">
+        <v>4200</v>
+      </c>
+      <c r="C965" t="n">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="D965" t="n">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="E965" t="n">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="F965"/>
+      <c r="G965" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/EPRB.MI.xlsx
+++ b/data/EPRB.MI.xlsx
@@ -22560,8 +22560,31 @@
       <c r="E965" t="n">
         <v>1.20000004768372</v>
       </c>
-      <c r="F965"/>
+      <c r="F965" t="n">
+        <v>1.20000004768372</v>
+      </c>
       <c r="G965" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B966" t="n">
+        <v>7350</v>
+      </c>
+      <c r="C966" t="n">
+        <v>1.20500004291534</v>
+      </c>
+      <c r="D966" t="n">
+        <v>1.17999994754791</v>
+      </c>
+      <c r="E966" t="n">
+        <v>1.19500005245209</v>
+      </c>
+      <c r="F966"/>
+      <c r="G966" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/EPRB.MI.xlsx
+++ b/data/EPRB.MI.xlsx
@@ -22583,8 +22583,31 @@
       <c r="E966" t="n">
         <v>1.19500005245209</v>
       </c>
-      <c r="F966"/>
+      <c r="F966" t="n">
+        <v>1.20000004768372</v>
+      </c>
       <c r="G966" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B967" t="n">
+        <v>350</v>
+      </c>
+      <c r="C967" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="D967" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="E967" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="F967"/>
+      <c r="G967" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/EPRB.MI.xlsx
+++ b/data/EPRB.MI.xlsx
@@ -22606,7 +22606,9 @@
       <c r="E967" t="n">
         <v>1.16999995708466</v>
       </c>
-      <c r="F967"/>
+      <c r="F967" t="n">
+        <v>1.16999995708466</v>
+      </c>
       <c r="G967" t="s">
         <v>7</v>
       </c>

--- a/data/EPRB.MI.xlsx
+++ b/data/EPRB.MI.xlsx
@@ -22636,6 +22636,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="969">
+      <c r="A969" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B969" t="n">
+        <v>0</v>
+      </c>
+      <c r="C969" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="D969" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="E969" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="F969" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="G969" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EPRB.MI.xlsx
+++ b/data/EPRB.MI.xlsx
@@ -22659,6 +22659,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="970">
+      <c r="A970" s="1" t="n">
+        <v>46308.2916666667</v>
+      </c>
+      <c r="B970" t="n">
+        <v>3500</v>
+      </c>
+      <c r="C970" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="D970" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="E970" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="F970" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="G970" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EPRB.MI.xlsx
+++ b/data/EPRB.MI.xlsx
@@ -22682,6 +22682,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="971">
+      <c r="A971" s="1" t="n">
+        <v>46309.2916666667</v>
+      </c>
+      <c r="B971" t="n">
+        <v>0</v>
+      </c>
+      <c r="C971" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="D971" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="E971" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="F971" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="G971" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EPRB.MI.xlsx
+++ b/data/EPRB.MI.xlsx
@@ -28595,6 +28595,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="974">
+      <c r="A974" t="s">
+        <v>9</v>
+      </c>
+      <c r="B974" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C974" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="D974" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="E974" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="F974" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="G974" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="H974" t="n">
+        <v>0</v>
+      </c>
+      <c r="I974" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EPRB.MI.xlsx
+++ b/data/EPRB.MI.xlsx
@@ -28624,6 +28624,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="975">
+      <c r="A975" t="s">
+        <v>9</v>
+      </c>
+      <c r="B975" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C975" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="D975" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="E975" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="F975" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="G975" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="H975" t="n">
+        <v>0</v>
+      </c>
+      <c r="I975" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="s">
+        <v>9</v>
+      </c>
+      <c r="B976" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C976" t="n">
+        <v>1.17999994754791</v>
+      </c>
+      <c r="D976" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="E976" t="n">
+        <v>1.17999994754791</v>
+      </c>
+      <c r="F976" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="G976" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="H976" t="n">
+        <v>1400</v>
+      </c>
+      <c r="I976" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EPRB.MI.xlsx
+++ b/data/EPRB.MI.xlsx
@@ -28682,6 +28682,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="977">
+      <c r="A977" t="s">
+        <v>9</v>
+      </c>
+      <c r="B977" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C977" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="D977" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="E977" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="F977" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="G977" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="H977" t="n">
+        <v>700</v>
+      </c>
+      <c r="I977" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EPRB.MI.xlsx
+++ b/data/EPRB.MI.xlsx
@@ -28711,6 +28711,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="978">
+      <c r="A978" t="s">
+        <v>9</v>
+      </c>
+      <c r="B978" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C978" t="n">
+        <v>1.17499995231628</v>
+      </c>
+      <c r="D978" t="n">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="E978" t="n">
+        <v>1.16499996185303</v>
+      </c>
+      <c r="F978" t="n">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="G978" t="n">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="H978" t="n">
+        <v>3850</v>
+      </c>
+      <c r="I978" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EPRB.MI.xlsx
+++ b/data/EPRB.MI.xlsx
@@ -28740,6 +28740,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="979">
+      <c r="A979" t="s">
+        <v>9</v>
+      </c>
+      <c r="B979" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C979" t="n">
+        <v>1.17499995231628</v>
+      </c>
+      <c r="D979" t="n">
+        <v>1.17499995231628</v>
+      </c>
+      <c r="E979" t="n">
+        <v>1.17499995231628</v>
+      </c>
+      <c r="F979" t="n">
+        <v>1.17499995231628</v>
+      </c>
+      <c r="G979" t="n">
+        <v>1.17499995231628</v>
+      </c>
+      <c r="H979" t="n">
+        <v>350</v>
+      </c>
+      <c r="I979" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EPRB.MI.xlsx
+++ b/data/EPRB.MI.xlsx
@@ -28769,6 +28769,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="980">
+      <c r="A980" t="s">
+        <v>9</v>
+      </c>
+      <c r="B980" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C980" t="n">
+        <v>1.17499995231628</v>
+      </c>
+      <c r="D980" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="E980" t="n">
+        <v>1.17499995231628</v>
+      </c>
+      <c r="F980" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="G980" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="H980" t="n">
+        <v>2100</v>
+      </c>
+      <c r="I980" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EPRB.MI.xlsx
+++ b/data/EPRB.MI.xlsx
@@ -28798,6 +28798,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="981">
+      <c r="A981" t="s">
+        <v>9</v>
+      </c>
+      <c r="B981" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C981" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="D981" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="E981" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="F981" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="G981" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="H981" t="n">
+        <v>0</v>
+      </c>
+      <c r="I981" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="s">
+        <v>9</v>
+      </c>
+      <c r="B982" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C982" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="D982" t="n">
+        <v>1.22000002861023</v>
+      </c>
+      <c r="E982" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="F982" t="n">
+        <v>1.22000002861023</v>
+      </c>
+      <c r="G982" t="n">
+        <v>1.22000002861023</v>
+      </c>
+      <c r="H982" t="n">
+        <v>1400</v>
+      </c>
+      <c r="I982" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EPRB.MI.xlsx
+++ b/data/EPRB.MI.xlsx
@@ -28856,6 +28856,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="983">
+      <c r="A983" t="s">
+        <v>9</v>
+      </c>
+      <c r="B983" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C983" t="n">
+        <v>1.19500005245209</v>
+      </c>
+      <c r="D983" t="n">
+        <v>1.19500005245209</v>
+      </c>
+      <c r="E983" t="n">
+        <v>1.19500005245209</v>
+      </c>
+      <c r="F983" t="n">
+        <v>1.19500005245209</v>
+      </c>
+      <c r="G983" t="n">
+        <v>1.19500005245209</v>
+      </c>
+      <c r="H983" t="n">
+        <v>700</v>
+      </c>
+      <c r="I983" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
